--- a/data/trans_camb/P45C_R1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,51</t>
+          <t>-1,39; 2,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,57</t>
+          <t>-2,59; 0,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,57</t>
+          <t>-1,95; 1,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,58</t>
+          <t>-2,05; 1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,49</t>
+          <t>-1,37; 2,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,18</t>
+          <t>-1,83; 1,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,46</t>
+          <t>-1,17; 1,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,98</t>
+          <t>-1,52; 0,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,85</t>
+          <t>-1,39; 0,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 412,28</t>
+          <t>-64,52; 291,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 365,7</t>
+          <t>-100,0; 269,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 236,72</t>
+          <t>-76,71; 167,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 346,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 485,33</t>
+          <t>-71,4; 625,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 277,15</t>
+          <t>-81,27; 389,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,87; 178,91</t>
+          <t>-57,84; 167,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 108,3</t>
+          <t>-72,38; 121,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,05; 102,52</t>
+          <t>-66,35; 95,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,85</t>
+          <t>-1,33; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,27</t>
+          <t>-1,31; 2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,82</t>
+          <t>-1,13; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,54</t>
+          <t>-0,94; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,62</t>
+          <t>-1,33; 2,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,09</t>
+          <t>-1,2; 3,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,08</t>
+          <t>-0,56; 1,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,71</t>
+          <t>-0,89; 1,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,32</t>
+          <t>-0,55; 2,4</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-85,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-92,27; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,88; 469,35</t>
+          <t>-53,35; 530,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 388,17</t>
+          <t>-63,6; 372,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,67; 423,56</t>
+          <t>-54,64; 469,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,29; 272,46</t>
+          <t>-40,52; 255,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 243,94</t>
+          <t>-55,98; 220,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 345,58</t>
+          <t>-44,02; 313,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,01</t>
+          <t>-3,62; 0,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; -1,19</t>
+          <t>-4,49; -1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,82</t>
+          <t>-3,65; 0,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,01</t>
+          <t>-5,7; 1,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -1,22</t>
+          <t>-8,03; -1,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,33</t>
+          <t>-5,71; 0,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,05</t>
+          <t>-3,2; -0,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -1,53</t>
+          <t>-4,31; -1,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,16</t>
+          <t>-3,37; 0,3</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,13; 13,94</t>
+          <t>-82,86; 16,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -40,01</t>
+          <t>-100,0; -51,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-86,15; 28,46</t>
+          <t>-85,99; 39,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-89,58; 105,58</t>
+          <t>-87,31; 103,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,19</t>
+          <t>-94,15; 86,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 0,85</t>
+          <t>-76,53; 1,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -57,45</t>
+          <t>-100,0; -63,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-82,06; 5,29</t>
+          <t>-84,7; 10,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,32</t>
+          <t>-1,46; 0,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,07</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,81</t>
+          <t>-1,18; 0,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,47</t>
+          <t>-2,27; 0,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,24</t>
+          <t>-2,89; -0,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,02</t>
+          <t>-2,65; 0,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,13</t>
+          <t>-1,46; 0,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; -0,43</t>
+          <t>-1,8; -0,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,31</t>
+          <t>-1,46; 0,23</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-71,19; 37,75</t>
+          <t>-68,47; 40,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,85; 11,7</t>
+          <t>-80,79; 9,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 81,08</t>
+          <t>-57,72; 91,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 42,05</t>
+          <t>-77,14; 52,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,59; -9,69</t>
+          <t>-88,5; -8,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,65; 5,22</t>
+          <t>-83,13; 10,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-62,07; 14,13</t>
+          <t>-64,01; 13,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,88; -26,48</t>
+          <t>-77,72; -22,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 30,13</t>
+          <t>-63,12; 17,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,74</t>
+          <t>-1,57; 1,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,02</t>
+          <t>-2,05; 0,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,07</t>
+          <t>-0,96; 3,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,84</t>
+          <t>-1,92; 0,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,63</t>
+          <t>-2,08; 0,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,83</t>
+          <t>-1,19; 1,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,73</t>
+          <t>-1,26; 0,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,39</t>
+          <t>-1,58; 0,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,61</t>
+          <t>-0,67; 1,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 390,75</t>
+          <t>-69,89; 352,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,23; 199,62</t>
+          <t>-82,14; 174,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,47; 547,35</t>
+          <t>-53,15; 512,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 110,33</t>
+          <t>-73,13; 117,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-81,6; 103,26</t>
+          <t>-79,58; 87,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,59; 216,65</t>
+          <t>-47,0; 188,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-56,85; 90,12</t>
+          <t>-58,57; 81,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-66,34; 52,06</t>
+          <t>-71,8; 53,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 173,14</t>
+          <t>-32,85; 169,95</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,05</t>
+          <t>-2,63; 0,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,35</t>
+          <t>-1,2; 3,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,99</t>
+          <t>-1,79; 5,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,41</t>
+          <t>-0,57; 1,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,8</t>
+          <t>-1,03; 0,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,1</t>
+          <t>-1,48; 0,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,09</t>
+          <t>-0,59; 1,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,01</t>
+          <t>-0,75; 1,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,69</t>
+          <t>-1,19; 0,84</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 771,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 169,63</t>
+          <t>-39,47; 165,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-62,35; 106,56</t>
+          <t>-61,71; 88,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-83,8; 24,59</t>
+          <t>-84,28; 16,75</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-39,97; 119,4</t>
+          <t>-38,57; 124,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 117,85</t>
+          <t>-49,63; 120,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 97,58</t>
+          <t>-77,88; 124,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,23</t>
+          <t>-1,01; 0,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,17</t>
+          <t>-1,35; -0,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,7</t>
+          <t>-0,81; 0,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,47</t>
+          <t>-0,75; 0,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,02</t>
+          <t>-1,19; -0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,28</t>
+          <t>-0,89; 0,31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,18</t>
+          <t>-0,68; 0,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; -0,28</t>
+          <t>-1,05; -0,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,28</t>
+          <t>-0,69; 0,29</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,37; 17,35</t>
+          <t>-49,05; 14,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,84; -12,0</t>
+          <t>-65,67; -8,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 53,05</t>
+          <t>-40,85; 54,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 34,4</t>
+          <t>-36,8; 32,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-56,78; 1,78</t>
+          <t>-59,37; -0,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 22,55</t>
+          <t>-43,78; 22,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 12,34</t>
+          <t>-35,65; 14,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -17,48</t>
+          <t>-54,72; -16,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 19,0</t>
+          <t>-35,18; 19,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,52</t>
+          <t>-1,38; 2,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,45</t>
+          <t>-2,49; 0,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,29</t>
+          <t>-1,5; 1,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,68</t>
+          <t>-1,98; 1,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,58</t>
+          <t>-1,15; 2,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,33</t>
+          <t>-2,18; 0,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,47</t>
+          <t>-1,16; 1,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,9</t>
+          <t>-1,42; 0,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,85</t>
+          <t>-1,43; 0,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,45%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,35%</t>
+          <t>-23,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,31%</t>
+          <t>-7,84%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,52; 291,61</t>
+          <t>-64,36; 317,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 269,55</t>
+          <t>-100,0; 136,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,71; 167,77</t>
+          <t>-64,88; 278,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,7; 311,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 625,3</t>
+          <t>-61,37; 576,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 389,03</t>
+          <t>-85,59; 284,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,84; 167,63</t>
+          <t>-58,26; 184,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 121,88</t>
+          <t>-71,87; 114,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,35; 95,16</t>
+          <t>-66,24; 109,72</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,8</t>
+          <t>-1,32; 2,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,09</t>
+          <t>-1,29; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,91</t>
+          <t>-1,35; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,67</t>
+          <t>-0,95; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,59</t>
+          <t>-1,5; 2,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,18</t>
+          <t>-0,98; 2,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,94</t>
+          <t>-0,5; 2,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,7</t>
+          <t>-0,83; 1,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,4</t>
+          <t>-0,61; 2,06</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-83,59; —</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 530,85</t>
+          <t>-54,1; 525,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,6; 372,61</t>
+          <t>-64,54; 378,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 469,45</t>
+          <t>-50,08; 356,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 255,6</t>
+          <t>-31,05; 317,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 220,59</t>
+          <t>-49,65; 270,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 313,56</t>
+          <t>-39,71; 279,0</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,29</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-0,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,07</t>
+          <t>-3,67; -0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -1,22</t>
+          <t>-4,55; -1,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,79</t>
+          <t>-2,55; 1,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 1,0</t>
+          <t>-5,36; 1,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -1,74</t>
+          <t>-7,15; -1,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 0,5</t>
+          <t>-6,03; 0,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -0,18</t>
+          <t>-3,42; -0,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -1,59</t>
+          <t>-4,45; -1,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,3</t>
+          <t>-2,64; 0,96</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-42,94%</t>
+          <t>-9,35%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-63,45%</t>
+          <t>-66,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-48,06%</t>
+          <t>-27,15%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,86; 16,57</t>
+          <t>-85,04; 8,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,32</t>
+          <t>-100,0; -34,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,99; 39,02</t>
+          <t>-61,82; 101,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-87,31; 103,34</t>
+          <t>-88,33; 104,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-94,15; 86,02</t>
+          <t>-100,0; 48,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,53; 1,52</t>
+          <t>-78,93; -3,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -63,97</t>
+          <t>-100,0; -55,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 10,31</t>
+          <t>-63,83; 51,33</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,35</t>
+          <t>-1,47; 0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,77; 0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,93</t>
+          <t>-1,24; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,61</t>
+          <t>-2,28; 0,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,36</t>
+          <t>-2,9; -0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,11</t>
+          <t>-2,18; 0,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,15</t>
+          <t>-1,54; 0,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; -0,35</t>
+          <t>-1,78; -0,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,23</t>
+          <t>-1,21; 0,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-9,83%</t>
+          <t>-9,6%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-51,49%</t>
+          <t>-33,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,76%</t>
+          <t>-20,36%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 40,08</t>
+          <t>-68,41; 57,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,79; 9,59</t>
+          <t>-79,62; 16,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 91,41</t>
+          <t>-58,66; 105,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-77,14; 52,68</t>
+          <t>-75,55; 62,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,5; -8,74</t>
+          <t>-88,45; -7,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,13; 10,29</t>
+          <t>-69,29; 52,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 13,97</t>
+          <t>-65,17; 12,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,72; -22,73</t>
+          <t>-78,36; -15,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 17,41</t>
+          <t>-51,47; 36,73</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,71</t>
+          <t>-1,57; 1,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,9</t>
+          <t>-1,91; 1,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,1</t>
+          <t>-1,34; 2,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,89</t>
+          <t>-1,81; 0,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,58</t>
+          <t>-2,1; 0,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,65</t>
+          <t>-0,88; 2,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,75</t>
+          <t>-1,39; 0,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,43</t>
+          <t>-1,6; 0,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,63</t>
+          <t>-0,59; 1,62</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-69,89; 352,09</t>
+          <t>-72,69; 341,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,14; 174,67</t>
+          <t>-83,92; 223,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,15; 512,57</t>
+          <t>-62,56; 433,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-73,13; 117,54</t>
+          <t>-74,07; 99,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,58; 87,94</t>
+          <t>-80,05; 83,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 188,27</t>
+          <t>-35,04; 274,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 81,43</t>
+          <t>-60,79; 76,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-71,8; 53,28</t>
+          <t>-69,95; 52,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 169,95</t>
+          <t>-27,74; 197,83</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,86</t>
+          <t>-2,35; 0,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,55</t>
+          <t>-1,35; 3,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,39</t>
+          <t>-1,78; 4,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,37</t>
+          <t>-0,61; 1,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,71</t>
+          <t>-1,04; 0,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,06</t>
+          <t>-1,41; -0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,06</t>
+          <t>-0,71; 1,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,05</t>
+          <t>-0,76; 1,01</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,84</t>
+          <t>-1,31; 0,4</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-52,6%</t>
+          <t>-56,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-37,41%</t>
+          <t>-42,97%</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>-84,05; 1088,38</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 165,47</t>
+          <t>-34,75; 162,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-61,71; 88,4</t>
+          <t>-61,59; 112,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 16,75</t>
+          <t>-85,04; 10,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 124,63</t>
+          <t>-42,02; 130,33</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 120,21</t>
+          <t>-47,66; 116,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 124,35</t>
+          <t>-80,38; 64,38</t>
         </is>
       </c>
     </row>
@@ -1930,14 +1930,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,54</t>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,21</t>
+          <t>-1,05; 0,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,35; -0,2</t>
+          <t>-1,4; -0,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,72</t>
+          <t>-0,69; 0,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,45</t>
+          <t>-0,65; 0,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,0</t>
+          <t>-1,21; 0,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,31</t>
+          <t>-0,75; 0,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,19</t>
+          <t>-0,7; 0,2</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; -0,25</t>
+          <t>-1,07; -0,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,29</t>
+          <t>-0,54; 0,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-6,11%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-17,8%</t>
+          <t>-13,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-12,1%</t>
+          <t>-6,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,05; 14,95</t>
+          <t>-49,27; 14,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,67; -8,99</t>
+          <t>-70,02; -14,31</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,85; 54,87</t>
+          <t>-34,01; 48,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 32,04</t>
+          <t>-33,25; 44,07</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-59,37; -0,25</t>
+          <t>-57,28; 1,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-43,78; 22,03</t>
+          <t>-37,68; 29,47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 14,22</t>
+          <t>-36,34; 14,23</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-54,72; -16,65</t>
+          <t>-54,82; -16,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 19,46</t>
+          <t>-28,69; 21,02</t>
         </is>
       </c>
     </row>
